--- a/backend/toolbox/股票扣非ttm估值.xlsx
+++ b/backend/toolbox/股票扣非ttm估值.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="447">
   <si>
     <t>个股</t>
   </si>
@@ -172,100 +172,1237 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>342.37</t>
-  </si>
-  <si>
-    <t>492.43</t>
-  </si>
-  <si>
-    <t>267.28</t>
-  </si>
-  <si>
-    <t>578.85</t>
-  </si>
-  <si>
-    <t>444.0</t>
-  </si>
-  <si>
-    <t>123.4</t>
-  </si>
-  <si>
-    <t>89.035</t>
-  </si>
-  <si>
-    <t>100.95</t>
-  </si>
-  <si>
-    <t>327.51</t>
-  </si>
-  <si>
-    <t>20260813</t>
-  </si>
-  <si>
-    <t>443.0</t>
+    <t>341.7</t>
+  </si>
+  <si>
+    <t>484.31</t>
+  </si>
+  <si>
+    <t>265.84</t>
+  </si>
+  <si>
+    <t>546.03</t>
+  </si>
+  <si>
+    <t>451.4</t>
+  </si>
+  <si>
+    <t>126.2</t>
+  </si>
+  <si>
+    <t>90.2</t>
+  </si>
+  <si>
+    <t>92.8</t>
+  </si>
+  <si>
+    <t>351.12</t>
+  </si>
+  <si>
+    <t>20260820</t>
+  </si>
+  <si>
+    <t>338.2</t>
+  </si>
+  <si>
+    <t>481.15</t>
+  </si>
+  <si>
+    <t>260.11</t>
+  </si>
+  <si>
+    <t>545.83</t>
+  </si>
+  <si>
+    <t>447.6</t>
+  </si>
+  <si>
+    <t>122.3</t>
+  </si>
+  <si>
+    <t>89.52</t>
+  </si>
+  <si>
+    <t>92.13</t>
+  </si>
+  <si>
+    <t>345.13</t>
+  </si>
+  <si>
+    <t>20260821</t>
+  </si>
+  <si>
+    <t>457.0</t>
   </si>
   <si>
     <t>123.0</t>
   </si>
   <si>
+    <t>341.75</t>
+  </si>
+  <si>
+    <t>483.24</t>
+  </si>
+  <si>
+    <t>258.63</t>
+  </si>
+  <si>
+    <t>549.9</t>
+  </si>
+  <si>
+    <t>88.38</t>
+  </si>
+  <si>
+    <t>90.07</t>
+  </si>
+  <si>
+    <t>362.86</t>
+  </si>
+  <si>
+    <t>20260822</t>
+  </si>
+  <si>
+    <t>445.6</t>
+  </si>
+  <si>
+    <t>112.0</t>
+  </si>
+  <si>
+    <t>20260824</t>
+  </si>
+  <si>
+    <t>440.0</t>
+  </si>
+  <si>
+    <t>112.5</t>
+  </si>
+  <si>
+    <t>344.59</t>
+  </si>
+  <si>
+    <t>487.31</t>
+  </si>
+  <si>
+    <t>262.07</t>
+  </si>
+  <si>
+    <t>559.02</t>
+  </si>
+  <si>
+    <t>438.6</t>
+  </si>
+  <si>
+    <t>113.3</t>
+  </si>
+  <si>
+    <t>87.07</t>
+  </si>
+  <si>
+    <t>87.26</t>
+  </si>
+  <si>
+    <t>348.95</t>
+  </si>
+  <si>
+    <t>20260825</t>
+  </si>
+  <si>
+    <t>339.1</t>
+  </si>
+  <si>
+    <t>496.37</t>
+  </si>
+  <si>
+    <t>260.28</t>
+  </si>
+  <si>
+    <t>576.14</t>
+  </si>
+  <si>
+    <t>448.8</t>
+  </si>
+  <si>
+    <t>115.9</t>
+  </si>
+  <si>
+    <t>86.74</t>
+  </si>
+  <si>
+    <t>88.24</t>
+  </si>
+  <si>
+    <t>345.82</t>
+  </si>
+  <si>
+    <t>20260827</t>
+  </si>
+  <si>
+    <t>447.4</t>
+  </si>
+  <si>
+    <t>116.4</t>
+  </si>
+  <si>
+    <t>342.88</t>
+  </si>
+  <si>
+    <t>513.53</t>
+  </si>
+  <si>
+    <t>266.43</t>
+  </si>
+  <si>
+    <t>578.02</t>
+  </si>
+  <si>
+    <t>455.2</t>
+  </si>
+  <si>
+    <t>113.9</t>
+  </si>
+  <si>
+    <t>85.69</t>
+  </si>
+  <si>
+    <t>89.47</t>
+  </si>
+  <si>
+    <t>348.75</t>
+  </si>
+  <si>
+    <t>20260829</t>
+  </si>
+  <si>
+    <t>335.41</t>
+  </si>
+  <si>
+    <t>507.29</t>
+  </si>
+  <si>
+    <t>259.77</t>
+  </si>
+  <si>
+    <t>572.34</t>
+  </si>
+  <si>
+    <t>442.8</t>
+  </si>
+  <si>
+    <t>110.2</t>
+  </si>
+  <si>
+    <t>84.0</t>
+  </si>
+  <si>
+    <t>89.51</t>
+  </si>
+  <si>
+    <t>367.95</t>
+  </si>
+  <si>
+    <t>20260901</t>
+  </si>
+  <si>
+    <t>332.03</t>
+  </si>
+  <si>
+    <t>501.02</t>
+  </si>
+  <si>
+    <t>254.92</t>
+  </si>
+  <si>
+    <t>578.54</t>
+  </si>
+  <si>
+    <t>438.0</t>
+  </si>
+  <si>
+    <t>108.5</t>
+  </si>
+  <si>
+    <t>83.17</t>
+  </si>
+  <si>
+    <t>88.97</t>
+  </si>
+  <si>
+    <t>356.09</t>
+  </si>
+  <si>
+    <t>20260902</t>
+  </si>
+  <si>
+    <t>333.78</t>
+  </si>
+  <si>
+    <t>496.82</t>
+  </si>
+  <si>
+    <t>254.98</t>
+  </si>
+  <si>
+    <t>592.85</t>
+  </si>
+  <si>
+    <t>433.0</t>
+  </si>
+  <si>
+    <t>107.5</t>
+  </si>
+  <si>
+    <t>82.25</t>
+  </si>
+  <si>
+    <t>90.05</t>
+  </si>
+  <si>
+    <t>357.01</t>
+  </si>
+  <si>
+    <t>20260903</t>
+  </si>
+  <si>
+    <t>335.31</t>
+  </si>
+  <si>
+    <t>499.7</t>
+  </si>
+  <si>
+    <t>258.51</t>
+  </si>
+  <si>
+    <t>616.77</t>
+  </si>
+  <si>
+    <t>110.1</t>
+  </si>
+  <si>
+    <t>82.21</t>
+  </si>
+  <si>
+    <t>95.8</t>
+  </si>
+  <si>
+    <t>354.08</t>
+  </si>
+  <si>
+    <t>20260905</t>
+  </si>
+  <si>
+    <t>438.4</t>
+  </si>
+  <si>
+    <t>109.6</t>
+  </si>
+  <si>
+    <t>20260907</t>
+  </si>
+  <si>
+    <t>436.8</t>
+  </si>
+  <si>
+    <t>108.7</t>
+  </si>
+  <si>
+    <t>20260908</t>
+  </si>
+  <si>
+    <t>335.1</t>
+  </si>
+  <si>
+    <t>492.09</t>
+  </si>
+  <si>
+    <t>257.05</t>
+  </si>
+  <si>
+    <t>616.13</t>
+  </si>
+  <si>
+    <t>435.4</t>
+  </si>
+  <si>
+    <t>109.5</t>
+  </si>
+  <si>
+    <t>79.415</t>
+  </si>
+  <si>
+    <t>104.6499</t>
+  </si>
+  <si>
+    <t>367.42</t>
+  </si>
+  <si>
+    <t>20260909</t>
+  </si>
+  <si>
+    <t>335.38</t>
+  </si>
+  <si>
+    <t>493.95</t>
+  </si>
+  <si>
+    <t>256.97</t>
+  </si>
+  <si>
+    <t>613.48</t>
+  </si>
+  <si>
+    <t>434.4</t>
+  </si>
+  <si>
+    <t>79.75</t>
+  </si>
+  <si>
+    <t>104.47</t>
+  </si>
+  <si>
+    <t>368.16</t>
+  </si>
+  <si>
+    <t>327.32</t>
+  </si>
+  <si>
+    <t>491.09</t>
+  </si>
+  <si>
+    <t>252.49</t>
+  </si>
+  <si>
+    <t>645.31</t>
+  </si>
+  <si>
+    <t>434.0</t>
+  </si>
+  <si>
+    <t>109.8</t>
+  </si>
+  <si>
+    <t>78.75</t>
+  </si>
+  <si>
+    <t>105.28</t>
+  </si>
+  <si>
+    <t>370.62</t>
+  </si>
+  <si>
+    <t>328.38</t>
+  </si>
+  <si>
+    <t>491.65</t>
+  </si>
+  <si>
+    <t>252.4</t>
+  </si>
+  <si>
+    <t>653.69</t>
+  </si>
+  <si>
+    <t>426.2</t>
+  </si>
+  <si>
+    <t>106.4</t>
+  </si>
+  <si>
+    <t>78.61</t>
+  </si>
+  <si>
+    <t>106.24</t>
+  </si>
+  <si>
+    <t>367.81</t>
+  </si>
+  <si>
+    <t>20260910</t>
+  </si>
+  <si>
+    <t>330.39</t>
+  </si>
+  <si>
+    <t>492.44</t>
+  </si>
+  <si>
+    <t>251.89</t>
+  </si>
+  <si>
+    <t>644.38</t>
+  </si>
+  <si>
+    <t>429.6</t>
+  </si>
+  <si>
+    <t>107.4</t>
+  </si>
+  <si>
+    <t>77.84</t>
+  </si>
+  <si>
+    <t>100.32</t>
+  </si>
+  <si>
+    <t>363.56</t>
+  </si>
+  <si>
+    <t>20260911</t>
+  </si>
+  <si>
+    <t>335.45</t>
+  </si>
+  <si>
+    <t>495.63</t>
+  </si>
+  <si>
+    <t>256.78</t>
+  </si>
+  <si>
+    <t>648.03</t>
+  </si>
+  <si>
+    <t>428.4</t>
+  </si>
+  <si>
+    <t>77.81</t>
+  </si>
+  <si>
+    <t>102.94</t>
+  </si>
+  <si>
+    <t>365.44</t>
+  </si>
+  <si>
+    <t>20260913</t>
+  </si>
+  <si>
+    <t>431.0</t>
+  </si>
+  <si>
+    <t>105.7</t>
+  </si>
+  <si>
+    <t>20260914</t>
+  </si>
+  <si>
+    <t>345.71</t>
+  </si>
+  <si>
+    <t>505.41</t>
+  </si>
+  <si>
+    <t>253.54</t>
+  </si>
+  <si>
+    <t>665.6</t>
+  </si>
+  <si>
     <t>441.0</t>
   </si>
   <si>
-    <t>121.9</t>
-  </si>
-  <si>
-    <t>343.94</t>
-  </si>
-  <si>
-    <t>496.88</t>
-  </si>
-  <si>
-    <t>265.13</t>
-  </si>
-  <si>
-    <t>594.97</t>
-  </si>
-  <si>
-    <t>440.0</t>
-  </si>
-  <si>
-    <t>119.9</t>
-  </si>
-  <si>
-    <t>84.17</t>
-  </si>
-  <si>
-    <t>104.56</t>
-  </si>
-  <si>
-    <t>339.96</t>
-  </si>
-  <si>
-    <t>20260814</t>
-  </si>
-  <si>
-    <t>343.54</t>
-  </si>
-  <si>
-    <t>495.4</t>
-  </si>
-  <si>
-    <t>262.65</t>
-  </si>
-  <si>
-    <t>589.85</t>
-  </si>
-  <si>
-    <t>84.79</t>
-  </si>
-  <si>
-    <t>102.5</t>
-  </si>
-  <si>
-    <t>342.27</t>
-  </si>
-  <si>
-    <t>20260815</t>
+    <t>107.7</t>
+  </si>
+  <si>
+    <t>79.38</t>
+  </si>
+  <si>
+    <t>97.19</t>
+  </si>
+  <si>
+    <t>358.97</t>
+  </si>
+  <si>
+    <t>20260915</t>
+  </si>
+  <si>
+    <t>440.6</t>
+  </si>
+  <si>
+    <t>341.43</t>
+  </si>
+  <si>
+    <t>497.12</t>
+  </si>
+  <si>
+    <t>248.42</t>
+  </si>
+  <si>
+    <t>670.24</t>
+  </si>
+  <si>
+    <t>445.0</t>
+  </si>
+  <si>
+    <t>106.5</t>
+  </si>
+  <si>
+    <t>78.08</t>
+  </si>
+  <si>
+    <t>97.14</t>
+  </si>
+  <si>
+    <t>356.58</t>
+  </si>
+  <si>
+    <t>20260916</t>
+  </si>
+  <si>
+    <t>438.8</t>
+  </si>
+  <si>
+    <t>107.0</t>
+  </si>
+  <si>
+    <t>434.8</t>
+  </si>
+  <si>
+    <t>106.7</t>
+  </si>
+  <si>
+    <t>433.4</t>
+  </si>
+  <si>
+    <t>106.2</t>
+  </si>
+  <si>
+    <t>343.68</t>
+  </si>
+  <si>
+    <t>497.75</t>
+  </si>
+  <si>
+    <t>251.19</t>
+  </si>
+  <si>
+    <t>682.31</t>
+  </si>
+  <si>
+    <t>425.8</t>
+  </si>
+  <si>
+    <t>108.4</t>
+  </si>
+  <si>
+    <t>77.73</t>
+  </si>
+  <si>
+    <t>108.8</t>
+  </si>
+  <si>
+    <t>366.2</t>
+  </si>
+  <si>
+    <t>20260918</t>
+  </si>
+  <si>
+    <t>419.0</t>
+  </si>
+  <si>
+    <t>109.3</t>
+  </si>
+  <si>
+    <t>352.1075</t>
+  </si>
+  <si>
+    <t>493.45</t>
+  </si>
+  <si>
+    <t>252.69</t>
+  </si>
+  <si>
+    <t>672.99</t>
+  </si>
+  <si>
+    <t>78.59</t>
+  </si>
+  <si>
+    <t>109.65</t>
+  </si>
+  <si>
+    <t>369.21</t>
+  </si>
+  <si>
+    <t>344.41</t>
+  </si>
+  <si>
+    <t>493.78</t>
+  </si>
+  <si>
+    <t>253.71</t>
+  </si>
+  <si>
+    <t>665.75</t>
+  </si>
+  <si>
+    <t>78.9</t>
+  </si>
+  <si>
+    <t>108.6</t>
+  </si>
+  <si>
+    <t>364.27</t>
+  </si>
+  <si>
+    <t>20260919</t>
+  </si>
+  <si>
+    <t>427.6</t>
+  </si>
+  <si>
+    <t>111.2</t>
+  </si>
+  <si>
+    <t>20260921</t>
+  </si>
+  <si>
+    <t>352.56</t>
+  </si>
+  <si>
+    <t>493.41</t>
+  </si>
+  <si>
+    <t>255.75</t>
+  </si>
+  <si>
+    <t>710.85</t>
+  </si>
+  <si>
+    <t>430.0</t>
+  </si>
+  <si>
+    <t>112.6</t>
+  </si>
+  <si>
+    <t>78.405</t>
+  </si>
+  <si>
+    <t>120.7</t>
+  </si>
+  <si>
+    <t>375.5667</t>
+  </si>
+  <si>
+    <t>350.87</t>
+  </si>
+  <si>
+    <t>501.61</t>
+  </si>
+  <si>
+    <t>258.45</t>
+  </si>
+  <si>
+    <t>741.245</t>
+  </si>
+  <si>
+    <t>451.6</t>
+  </si>
+  <si>
+    <t>114.8</t>
+  </si>
+  <si>
+    <t>79.295</t>
+  </si>
+  <si>
+    <t>121.78</t>
+  </si>
+  <si>
+    <t>375.3</t>
+  </si>
+  <si>
+    <t>20260922</t>
+  </si>
+  <si>
+    <t>347.41</t>
+  </si>
+  <si>
+    <t>498.0</t>
+  </si>
+  <si>
+    <t>736.595</t>
+  </si>
+  <si>
+    <t>80.35</t>
+  </si>
+  <si>
+    <t>123.86</t>
+  </si>
+  <si>
+    <t>378.9</t>
+  </si>
+  <si>
+    <t>20260923</t>
+  </si>
+  <si>
+    <t>334.261</t>
+  </si>
+  <si>
+    <t>494.75</t>
+  </si>
+  <si>
+    <t>246.155</t>
+  </si>
+  <si>
+    <t>764.4899</t>
+  </si>
+  <si>
+    <t>110.0</t>
+  </si>
+  <si>
+    <t>78.1</t>
+  </si>
+  <si>
+    <t>122.52</t>
+  </si>
+  <si>
+    <t>376.42</t>
+  </si>
+  <si>
+    <t>20260924</t>
+  </si>
+  <si>
+    <t>339.01</t>
+  </si>
+  <si>
+    <t>497.93</t>
+  </si>
+  <si>
+    <t>249.38</t>
+  </si>
+  <si>
+    <t>777.59</t>
+  </si>
+  <si>
+    <t>420.0</t>
+  </si>
+  <si>
+    <t>106.0</t>
+  </si>
+  <si>
+    <t>78.2</t>
+  </si>
+  <si>
+    <t>127.39</t>
+  </si>
+  <si>
+    <t>377.94</t>
+  </si>
+  <si>
+    <t>20260925</t>
+  </si>
+  <si>
+    <t>341.08</t>
+  </si>
+  <si>
+    <t>516.17</t>
+  </si>
+  <si>
+    <t>249.67</t>
+  </si>
+  <si>
+    <t>751.66</t>
+  </si>
+  <si>
+    <t>436.6</t>
+  </si>
+  <si>
+    <t>77.57</t>
+  </si>
+  <si>
+    <t>372.11</t>
+  </si>
+  <si>
+    <t>20260926</t>
+  </si>
+  <si>
+    <t>337.32</t>
+  </si>
+  <si>
+    <t>508.96</t>
+  </si>
+  <si>
+    <t>246.67</t>
+  </si>
+  <si>
+    <t>738.79</t>
+  </si>
+  <si>
+    <t>106.6</t>
+  </si>
+  <si>
+    <t>77.5</t>
+  </si>
+  <si>
+    <t>115.93</t>
+  </si>
+  <si>
+    <t>352.84</t>
+  </si>
+  <si>
+    <t>20260930</t>
+  </si>
+  <si>
+    <t>340.74</t>
+  </si>
+  <si>
+    <t>512.9</t>
+  </si>
+  <si>
+    <t>249.15</t>
+  </si>
+  <si>
+    <t>725.18</t>
+  </si>
+  <si>
+    <t>77.94</t>
+  </si>
+  <si>
+    <t>120.23</t>
+  </si>
+  <si>
+    <t>354.81</t>
+  </si>
+  <si>
+    <t>20261001</t>
+  </si>
+  <si>
+    <t>344.83</t>
+  </si>
+  <si>
+    <t>533.085</t>
+  </si>
+  <si>
+    <t>255.29</t>
+  </si>
+  <si>
+    <t>741.975</t>
+  </si>
+  <si>
+    <t>428.2</t>
+  </si>
+  <si>
+    <t>108.2</t>
+  </si>
+  <si>
+    <t>77.875</t>
+  </si>
+  <si>
+    <t>114.3507</t>
+  </si>
+  <si>
+    <t>380.41</t>
+  </si>
+  <si>
+    <t>20261006</t>
+  </si>
+  <si>
+    <t>347.37</t>
+  </si>
+  <si>
+    <t>529.76</t>
+  </si>
+  <si>
+    <t>259.92</t>
+  </si>
+  <si>
+    <t>721.31</t>
+  </si>
+  <si>
+    <t>411.4</t>
+  </si>
+  <si>
+    <t>104.3</t>
+  </si>
+  <si>
+    <t>78.5</t>
+  </si>
+  <si>
+    <t>113.12</t>
+  </si>
+  <si>
+    <t>377.81</t>
+  </si>
+  <si>
+    <t>20261008</t>
+  </si>
+  <si>
+    <t>347.86</t>
+  </si>
+  <si>
+    <t>535.07</t>
+  </si>
+  <si>
+    <t>262.43</t>
+  </si>
+  <si>
+    <t>718.67</t>
+  </si>
+  <si>
+    <t>81.35</t>
+  </si>
+  <si>
+    <t>104.7</t>
+  </si>
+  <si>
+    <t>382.7</t>
+  </si>
+  <si>
+    <t>20261012</t>
+  </si>
+  <si>
+    <t>348.97</t>
+  </si>
+  <si>
+    <t>541.15</t>
+  </si>
+  <si>
+    <t>259.53</t>
+  </si>
+  <si>
+    <t>742.96</t>
+  </si>
+  <si>
+    <t>80.92</t>
+  </si>
+  <si>
+    <t>101.35</t>
+  </si>
+  <si>
+    <t>378.03</t>
+  </si>
+  <si>
+    <t>20261013</t>
+  </si>
+  <si>
+    <t>352.325</t>
+  </si>
+  <si>
+    <t>545.97</t>
+  </si>
+  <si>
+    <t>260.71</t>
+  </si>
+  <si>
+    <t>762.445</t>
+  </si>
+  <si>
+    <t>425.2</t>
+  </si>
+  <si>
+    <t>107.2</t>
+  </si>
+  <si>
+    <t>100.255</t>
+  </si>
+  <si>
+    <t>376.54</t>
+  </si>
+  <si>
+    <t>349.52</t>
+  </si>
+  <si>
+    <t>543.45</t>
+  </si>
+  <si>
+    <t>258.58</t>
+  </si>
+  <si>
+    <t>762.5</t>
+  </si>
+  <si>
+    <t>426.0</t>
+  </si>
+  <si>
+    <t>81.96</t>
+  </si>
+  <si>
+    <t>102.81</t>
+  </si>
+  <si>
+    <t>375.23</t>
+  </si>
+  <si>
+    <t>20261014</t>
+  </si>
+  <si>
+    <t>343.65</t>
+  </si>
+  <si>
+    <t>533.69</t>
+  </si>
+  <si>
+    <t>254.08</t>
+  </si>
+  <si>
+    <t>737.54</t>
+  </si>
+  <si>
+    <t>423.4</t>
+  </si>
+  <si>
+    <t>110.5</t>
+  </si>
+  <si>
+    <t>81.45</t>
+  </si>
+  <si>
+    <t>98.12</t>
+  </si>
+  <si>
+    <t>367.16</t>
+  </si>
+  <si>
+    <t>20261015</t>
+  </si>
+  <si>
+    <t>420.6</t>
+  </si>
+  <si>
+    <t>418.6</t>
+  </si>
+  <si>
+    <t>105.8</t>
+  </si>
+  <si>
+    <t>343.665</t>
+  </si>
+  <si>
+    <t>537.14</t>
+  </si>
+  <si>
+    <t>250.03</t>
+  </si>
+  <si>
+    <t>731.86</t>
+  </si>
+  <si>
+    <t>417.8</t>
+  </si>
+  <si>
+    <t>82.51</t>
+  </si>
+  <si>
+    <t>93.165</t>
+  </si>
+  <si>
+    <t>359.6</t>
+  </si>
+  <si>
+    <t>344.91</t>
+  </si>
+  <si>
+    <t>539.44</t>
+  </si>
+  <si>
+    <t>254.76</t>
+  </si>
+  <si>
+    <t>736.72</t>
+  </si>
+  <si>
+    <t>82.42</t>
+  </si>
+  <si>
+    <t>95.37</t>
+  </si>
+  <si>
+    <t>362.44</t>
+  </si>
+  <si>
+    <t>20261016</t>
+  </si>
+  <si>
+    <t>336.91</t>
+  </si>
+  <si>
+    <t>529.05</t>
+  </si>
+  <si>
+    <t>250.0</t>
+  </si>
+  <si>
+    <t>709.325</t>
+  </si>
+  <si>
+    <t>80.97</t>
+  </si>
+  <si>
+    <t>89.85</t>
+  </si>
+  <si>
+    <t>354.72</t>
+  </si>
+  <si>
+    <t>20261017</t>
+  </si>
+  <si>
+    <t>20261019</t>
+  </si>
+  <si>
+    <t>340.16</t>
+  </si>
+  <si>
+    <t>533.52</t>
+  </si>
+  <si>
+    <t>262.45</t>
+  </si>
+  <si>
+    <t>705.44</t>
+  </si>
+  <si>
+    <t>409.8</t>
+  </si>
+  <si>
+    <t>105.3</t>
+  </si>
+  <si>
+    <t>81.39</t>
+  </si>
+  <si>
+    <t>92.03</t>
+  </si>
+  <si>
+    <t>368.06</t>
+  </si>
+  <si>
+    <t>20261020</t>
+  </si>
+  <si>
+    <t>320.76</t>
+  </si>
+  <si>
+    <t>521.08</t>
+  </si>
+  <si>
+    <t>250.38</t>
+  </si>
+  <si>
+    <t>648.85</t>
+  </si>
+  <si>
+    <t>375.0</t>
+  </si>
+  <si>
+    <t>98.0</t>
+  </si>
+  <si>
+    <t>79.17</t>
+  </si>
+  <si>
+    <t>85.49</t>
+  </si>
+  <si>
+    <t>374.58</t>
+  </si>
+  <si>
+    <t>20261023</t>
+  </si>
+  <si>
+    <t>381.8</t>
+  </si>
+  <si>
+    <t>98.5</t>
   </si>
 </sst>
 </file>
@@ -791,7 +1928,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>60</v>
+        <v>435</v>
       </c>
       <c r="E2">
         <v>122.3</v>
@@ -830,7 +1967,7 @@
         <v>12</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>61</v>
+        <v>436</v>
       </c>
       <c r="E3">
         <v>74.28</v>
@@ -869,7 +2006,7 @@
         <v>13</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>62</v>
+        <v>437</v>
       </c>
       <c r="E4">
         <v>107.57</v>
@@ -908,7 +2045,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>63</v>
+        <v>438</v>
       </c>
       <c r="E5">
         <v>25.38</v>
@@ -949,7 +2086,7 @@
         <v>29</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>54</v>
+        <v>445</v>
       </c>
       <c r="E6">
         <v>90.93</v>
@@ -988,7 +2125,7 @@
         <v>30</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>55</v>
+        <v>446</v>
       </c>
       <c r="E7">
         <v>191.77</v>
@@ -997,10 +2134,13 @@
         <f t="shared" si="2"/>
       </c>
       <c r="G7" s="11">
-        <f t="shared" ref="G6:G8" si="3">SUM(J7:M7)</f>
+        <f>SUM(I7:L7)</f>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="1"/>
+      </c>
+      <c r="I7" s="16">
+        <v>207.15</v>
       </c>
       <c r="J7" s="16">
         <v>0.86</v>
@@ -1024,7 +2164,7 @@
         <v>33</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>64</v>
+        <v>441</v>
       </c>
       <c r="E8">
         <v>14.23</v>
@@ -1033,7 +2173,7 @@
         <f t="shared" si="2"/>
       </c>
       <c r="G8" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="G7:G8" si="3">SUM(J8:M8)</f>
       </c>
       <c r="H8" s="12">
         <f t="shared" si="1"/>
@@ -1062,7 +2202,7 @@
         <v>24</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>65</v>
+        <v>442</v>
       </c>
       <c r="E9">
         <v>50.26</v>
@@ -1103,7 +2243,7 @@
         <v>27</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>66</v>
+        <v>443</v>
       </c>
       <c r="E10">
         <v>39.5</v>
@@ -1141,7 +2281,7 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>444</v>
       </c>
       <c r="F12" s="3"/>
     </row>
